--- a/Data/GP2_INITIAL_WEIGHT.xlsx
+++ b/Data/GP2_INITIAL_WEIGHT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A8DD93-26CD-4404-91CA-481E9A7214A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD2CE71-53AD-4FCE-BE3B-A09494CD7914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D55D7C9-8C16-44D8-8BF6-2ADAB78CA17C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="12">
   <si>
     <t>sex</t>
   </si>
@@ -63,6 +63,15 @@
   </si>
   <si>
     <t>T4</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>SE</t>
   </si>
 </sst>
 </file>
@@ -452,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE882B2-CB05-4E34-88CB-C2794A9869F7}">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.08984375" bestFit="1" customWidth="1"/>
@@ -1350,7 +1359,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>8</v>
       </c>
@@ -1359,6 +1368,30 @@
       </c>
       <c r="C81" s="2">
         <v>322</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E82">
+        <v>468.7</v>
+      </c>
+      <c r="F82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E83">
+        <v>136.14404136795707</v>
+      </c>
+      <c r="F83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E84">
+        <v>15.221366561514772</v>
+      </c>
+      <c r="F84" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
